--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -656,61 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -723,35 +724,38 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>529000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -764,35 +768,38 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>282900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,35 +812,38 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>246100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -846,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,35 +876,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E12" s="3">
         <v>400</v>
       </c>
       <c r="F12" s="3">
+        <v>400</v>
+      </c>
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>400</v>
       </c>
       <c r="I12" s="3">
         <v>400</v>
       </c>
       <c r="J12" s="3">
+        <v>400</v>
+      </c>
+      <c r="K12" s="3">
         <v>369000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +962,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,8 +1006,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,18 +1026,18 @@
       <c r="G15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>1600</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,35 +1067,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2900</v>
+        <v>4100</v>
       </c>
       <c r="E17" s="3">
         <v>2900</v>
       </c>
       <c r="F17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>685700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1082,35 +1109,38 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-156700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1123,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,35 +1173,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,35 +1215,38 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-163400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1259,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1263,35 +1303,38 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-163500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,8 +1347,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1345,8 +1391,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,35 +1435,38 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-163500</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,35 +1479,38 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-163500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,8 +1523,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,35 +1699,38 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,35 +1743,38 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-163500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1787,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,35 +1831,38 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-163500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1796,40 +1875,43 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1924,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,29 +1962,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,31 +2004,34 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>11000</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1958,29 +2048,32 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,29 +2092,32 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,28 +2136,31 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2081,29 +2180,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E46" s="3">
         <v>9700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1500</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,8 +2224,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2163,28 +2268,31 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
         <v>900</v>
       </c>
       <c r="F48" s="3">
+        <v>900</v>
+      </c>
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
       <c r="H48" s="3">
         <v>0</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2204,8 +2312,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,8 +2444,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2342,14 +2462,14 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,29 +2532,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E54" s="3">
         <v>10700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,29 +2614,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>500</v>
+      </c>
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,29 +2656,32 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2566,29 +2700,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,29 +2744,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1800</v>
+        <v>3100</v>
       </c>
       <c r="E60" s="3">
         <v>1800</v>
       </c>
       <c r="F60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,29 +2788,32 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
         <v>900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1100</v>
       </c>
       <c r="F61" s="3">
         <v>1100</v>
       </c>
       <c r="G61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H61" s="3">
         <v>1800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2689,8 +2832,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2698,20 +2844,20 @@
         <v>800</v>
       </c>
       <c r="E62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>900</v>
       </c>
       <c r="G62" s="3">
+        <v>900</v>
+      </c>
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,29 +3008,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,29 +3246,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-8200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,29 +3422,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3280,8 +3466,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,40 +3510,43 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3367,35 +3559,38 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-163500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3408,8 +3603,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,8 +3623,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3451,8 +3650,8 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,35 +3885,38 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3929,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,23 +3949,24 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3758,8 +3979,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,35 +4079,38 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3893,8 +4123,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,35 +4317,38 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>14400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4115,37 +4361,40 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4156,34 +4405,37 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -4195,6 +4447,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -656,65 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -727,38 +728,41 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>529000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -771,8 +775,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,29 +787,29 @@
         <v>1500</v>
       </c>
       <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3">
         <v>600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>282900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,38 +822,41 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>246100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -859,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,38 +890,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
-      </c>
-      <c r="E12" s="3">
-        <v>400</v>
       </c>
       <c r="F12" s="3">
         <v>400</v>
       </c>
       <c r="G12" s="3">
+        <v>400</v>
+      </c>
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>400</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
+        <v>400</v>
+      </c>
+      <c r="L12" s="3">
         <v>369000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,8 +982,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1009,8 +1029,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,18 +1052,18 @@
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>1600</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1076,11 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,38 +1094,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
         <v>4100</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2900</v>
       </c>
       <c r="F17" s="3">
         <v>2900</v>
       </c>
       <c r="G17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>685700</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1112,38 +1139,41 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-156700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1156,8 +1186,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,38 +1207,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1218,38 +1252,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-163400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,8 +1299,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1306,38 +1346,41 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-163500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,31 +1393,34 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1394,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,38 +1487,41 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-163500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,38 +1534,41 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-163500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,8 +1581,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,38 +1769,41 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1746,38 +1816,41 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-163500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1790,8 +1863,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,38 +1910,41 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-163500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,43 +1957,46 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +2009,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,32 +2049,33 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,34 +2094,37 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2051,32 +2141,35 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,32 +2188,35 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2139,8 +2235,11 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2156,14 +2255,14 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2183,32 +2282,35 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E46" s="3">
         <v>10300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,8 +2329,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2271,31 +2376,34 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>900</v>
       </c>
       <c r="F48" s="3">
         <v>900</v>
       </c>
       <c r="G48" s="3">
+        <v>900</v>
+      </c>
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2315,8 +2423,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2359,8 +2470,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,8 +2564,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2465,14 +2585,14 @@
         <v>200</v>
       </c>
       <c r="H52" s="3">
+        <v>200</v>
+      </c>
+      <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,32 +2658,35 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E54" s="3">
         <v>11300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2705,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,32 +2745,33 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
       </c>
       <c r="H57" s="3">
         <v>500</v>
       </c>
       <c r="I57" s="3">
+        <v>500</v>
+      </c>
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,32 +2790,35 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,32 +2837,35 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,32 +2884,35 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3100</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1800</v>
       </c>
       <c r="F60" s="3">
         <v>1800</v>
       </c>
       <c r="G60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,32 +2931,35 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1100</v>
       </c>
       <c r="G61" s="3">
         <v>1100</v>
       </c>
       <c r="H61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2835,8 +2978,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2847,20 +2993,20 @@
         <v>800</v>
       </c>
       <c r="F62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G62" s="3">
         <v>900</v>
       </c>
       <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3025,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,32 +3166,35 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3500</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3213,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,32 +3420,35 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-10900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-6800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3467,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,32 +3608,35 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3655,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,43 +3702,46 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3562,38 +3754,41 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-163500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,8 +3801,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,8 +3822,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3653,8 +3852,8 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3668,8 +3867,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,38 +4102,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,8 +4149,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,26 +4170,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3982,8 +4203,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -3994,8 +4215,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,38 +4309,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,8 +4356,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,38 +4563,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>14400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4364,8 +4610,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,13 +4640,13 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4408,37 +4657,40 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4450,6 +4702,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -663,13 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.140625" style="1"/>
@@ -693,22 +691,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -737,25 +735,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3400</v>
+        <v>1700</v>
       </c>
       <c r="E8" s="3">
-        <v>3600</v>
+        <v>1700</v>
       </c>
       <c r="F8" s="3">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="G8" s="3">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H8" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J8" s="3">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="K8" s="3">
         <v>500</v>
@@ -784,25 +782,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="F9" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G9" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="H9" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>600</v>
       </c>
       <c r="K9" s="3">
         <v>200</v>
@@ -831,25 +829,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="E10" s="3">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
-        <v>400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>300</v>
-      </c>
       <c r="I10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>700</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
@@ -897,25 +895,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>300</v>
       </c>
-      <c r="E12" s="3">
-        <v>600</v>
-      </c>
-      <c r="F12" s="3">
-        <v>400</v>
-      </c>
       <c r="G12" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H12" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="I12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J12" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>400</v>
@@ -990,11 +988,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1002,14 +1000,14 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1037,23 +1035,23 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1101,25 +1099,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3400</v>
+        <v>1700</v>
       </c>
       <c r="E17" s="3">
-        <v>4100</v>
+        <v>1700</v>
       </c>
       <c r="F17" s="3">
-        <v>2900</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="3">
-        <v>2900</v>
+        <v>2000</v>
       </c>
       <c r="H17" s="3">
-        <v>3300</v>
+        <v>1400</v>
       </c>
       <c r="I17" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="J17" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="K17" s="3">
         <v>700</v>
@@ -1151,22 +1149,22 @@
         <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>-2400</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="H18" s="3">
-        <v>-2300</v>
+        <v>-1200</v>
       </c>
       <c r="I18" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K18" s="3">
         <v>-200</v>
@@ -1213,23 +1211,23 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-200</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1261,25 +1259,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
-        <v>-2200</v>
+        <v>-200</v>
       </c>
       <c r="G21" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H21" s="3">
-        <v>-2300</v>
+        <v>-1200</v>
       </c>
       <c r="I21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-100</v>
       </c>
       <c r="K21" s="3">
         <v>-500</v>
@@ -1307,26 +1305,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1358,22 +1356,22 @@
         <v>100</v>
       </c>
       <c r="E23" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G23" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H23" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I23" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J23" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K23" s="3">
         <v>-500</v>
@@ -1499,22 +1497,22 @@
         <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F26" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G26" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H26" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I26" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J26" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K26" s="3">
         <v>-500</v>
@@ -1546,22 +1544,22 @@
         <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F27" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G27" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H27" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I27" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J27" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K27" s="3">
         <v>-500</v>
@@ -1777,23 +1775,23 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>200</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -1828,22 +1826,22 @@
         <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G33" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H33" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I33" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J33" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K33" s="3">
         <v>-500</v>
@@ -1922,22 +1920,22 @@
         <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G35" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H35" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I35" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J35" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K35" s="3">
         <v>-500</v>
@@ -1974,22 +1972,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2059,22 +2057,22 @@
         <v>800</v>
       </c>
       <c r="E41" s="3">
+        <v>800</v>
+      </c>
+      <c r="F41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J41" s="3">
         <v>200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -2106,22 +2104,22 @@
         <v>3000</v>
       </c>
       <c r="E42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H42" s="3">
         <v>5100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J42" s="3">
         <v>9100</v>
-      </c>
-      <c r="H42" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2153,22 +2151,22 @@
         <v>4000</v>
       </c>
       <c r="E43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J43" s="3">
         <v>2000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>600</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1100</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2200,22 +2198,22 @@
         <v>1900</v>
       </c>
       <c r="E44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F44" s="3">
         <v>2000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J44" s="3">
         <v>1000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>400</v>
-      </c>
-      <c r="J44" s="3">
-        <v>300</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -2258,11 +2256,11 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2294,22 +2292,22 @@
         <v>9700</v>
       </c>
       <c r="E46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F46" s="3">
         <v>10300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H46" s="3">
         <v>9700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J46" s="3">
         <v>12300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>13100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>1500</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2337,26 +2335,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2388,22 +2386,22 @@
         <v>1000</v>
       </c>
       <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>800</v>
+      </c>
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
-        <v>800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2588,10 +2586,10 @@
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2670,22 +2668,22 @@
         <v>10900</v>
       </c>
       <c r="E54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F54" s="3">
         <v>11300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="H54" s="3">
         <v>10700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J54" s="3">
         <v>13400</v>
-      </c>
-      <c r="H54" s="3">
-        <v>14100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1900</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2755,22 +2753,22 @@
         <v>900</v>
       </c>
       <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>700</v>
+      </c>
+      <c r="J57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2802,22 +2800,22 @@
         <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F58" s="3">
+        <v>600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>600</v>
+      </c>
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2849,22 +2847,22 @@
         <v>1200</v>
       </c>
       <c r="E59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
-        <v>700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
-      </c>
       <c r="I59" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J59" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2896,22 +2894,22 @@
         <v>2700</v>
       </c>
       <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2000</v>
-      </c>
       <c r="J60" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2940,7 +2938,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>600</v>
@@ -2949,16 +2947,16 @@
         <v>900</v>
       </c>
       <c r="G61" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="H61" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="J61" s="3">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2987,25 +2985,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F62" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="H62" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3178,22 +3176,22 @@
         <v>3800</v>
       </c>
       <c r="E66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F66" s="3">
         <v>4400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H66" s="3">
         <v>3400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J66" s="3">
         <v>3800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3432,22 +3430,22 @@
         <v>-10800</v>
       </c>
       <c r="E72" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-10900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="H72" s="3">
         <v>-10500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J72" s="3">
         <v>-8200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-3700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3620,22 +3618,22 @@
         <v>7100</v>
       </c>
       <c r="E76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H76" s="3">
         <v>7300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J76" s="3">
         <v>9600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>11000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>-1600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3719,22 +3717,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -3766,22 +3764,22 @@
         <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>-400</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3">
-        <v>-2300</v>
+        <v>-200</v>
       </c>
       <c r="G81" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="H81" s="3">
-        <v>-2300</v>
+        <v>-1100</v>
       </c>
       <c r="I81" s="3">
-        <v>-800</v>
+        <v>-1100</v>
       </c>
       <c r="J81" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="K81" s="3">
         <v>-500</v>
@@ -4111,25 +4109,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-800</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
@@ -4177,25 +4175,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4321,22 +4319,22 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>3900</v>
+        <v>900</v>
       </c>
       <c r="G94" s="3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="H94" s="3">
-        <v>-11100</v>
+        <v>2000</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
@@ -4383,26 +4381,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4572,25 +4570,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>14400</v>
-      </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>300</v>
@@ -4618,26 +4616,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4666,25 +4664,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1200</v>
+        <v>-600</v>
       </c>
       <c r="E102" s="3">
-        <v>300</v>
+        <v>-600</v>
       </c>
       <c r="F102" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>800</v>
+      </c>
+      <c r="J102" s="3">
         <v>-100</v>
-      </c>
-      <c r="H102" s="3">
-        <v>300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>100</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -656,70 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,44 +730,50 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>529000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,16 +783,22 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F9" s="3">
         <v>700</v>
@@ -794,26 +807,26 @@
         <v>700</v>
       </c>
       <c r="H9" s="3">
+        <v>700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>700</v>
+      </c>
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>282900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,16 +836,22 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E10" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F10" s="3">
         <v>1000</v>
@@ -841,26 +860,26 @@
         <v>1000</v>
       </c>
       <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>246100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,8 +889,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,44 +914,46 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
       </c>
       <c r="K12" s="3">
+        <v>200</v>
+      </c>
+      <c r="L12" s="3">
+        <v>200</v>
+      </c>
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>369000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +963,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,8 +1016,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -994,26 +1033,26 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1030,8 +1069,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1060,14 +1105,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>1600</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1077,8 +1122,14 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,44 +1144,46 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>685700</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,44 +1193,50 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-156700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1246,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,44 +1271,46 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-6800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,44 +1320,50 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-163400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1373,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1326,11 +1405,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1347,44 +1426,50 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-163500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,8 +1479,14 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1420,11 +1511,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1441,8 +1532,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,44 +1585,50 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-163500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1535,44 +1638,50 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-163500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1691,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1744,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1797,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1850,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,44 +1903,50 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>6800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,44 +1956,50 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-163500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +2009,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,44 +2062,50 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-163500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,49 +2115,55 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2010,8 +2173,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2198,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,38 +2219,40 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,40 +2268,46 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>3000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>3000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>5100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2142,38 +2321,44 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F43" s="3">
         <v>4000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,38 +2374,44 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F44" s="3">
         <v>1900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2236,8 +2427,14 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2283,38 +2480,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F46" s="3">
         <v>9700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>9700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,8 +2533,14 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2356,11 +2565,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2377,37 +2586,43 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
-      </c>
-      <c r="H48" s="3">
-        <v>900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>900</v>
       </c>
       <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+      <c r="K48" s="3">
+        <v>900</v>
+      </c>
+      <c r="L48" s="3">
+        <v>900</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2424,8 +2639,14 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2471,8 +2692,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2745,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,8 +2798,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2591,11 +2830,11 @@
       <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>200</v>
+      </c>
+      <c r="L52" s="3">
+        <v>200</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2612,8 +2851,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,38 +2904,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F54" s="3">
         <v>10900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2957,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2982,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,38 +3003,40 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,16 +3052,22 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>600</v>
@@ -2809,20 +3076,20 @@
         <v>600</v>
       </c>
       <c r="H58" s="3">
+        <v>600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,37 +3105,43 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2885,37 +3158,43 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1800</v>
       </c>
       <c r="J60" s="3">
         <v>1800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L60" s="3">
+        <v>1800</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
@@ -2932,38 +3211,44 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2979,8 +3264,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2991,25 +3282,25 @@
         <v>400</v>
       </c>
       <c r="F62" s="3">
+        <v>400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>400</v>
+      </c>
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
+        <v>400</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -3026,8 +3317,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3370,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3423,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,38 +3476,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3529,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3554,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3603,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3656,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3374,8 +3709,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,38 +3762,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-10800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-10800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-10900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-10500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-10500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3815,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3868,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3921,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,38 +3974,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +4027,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,49 +4080,55 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3755,44 +4138,50 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-163500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +4191,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,8 +4216,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3853,11 +4250,11 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -3868,8 +4265,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4318,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4371,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4424,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4477,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,44 +4530,50 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4150,8 +4583,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,23 +4608,25 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -4193,22 +4634,22 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4657,14 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4710,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,44 +4763,50 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,8 +4816,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4841,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4402,11 +4869,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4423,8 +4890,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4943,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4996,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,8 +5049,14 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4576,32 +5067,32 @@
         <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4611,8 +5102,14 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4637,20 +5134,20 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4658,43 +5155,49 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -4703,6 +5206,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="92">
   <si>
     <t>MTEK</t>
   </si>
@@ -656,85 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,56 +745,62 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>529000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,28 +810,34 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>700</v>
       </c>
       <c r="J9" s="3">
         <v>700</v>
@@ -833,26 +846,26 @@
         <v>700</v>
       </c>
       <c r="L9" s="3">
+        <v>700</v>
+      </c>
+      <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>282900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,28 +875,34 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1000</v>
       </c>
       <c r="J10" s="3">
         <v>1000</v>
@@ -892,26 +911,26 @@
         <v>1000</v>
       </c>
       <c r="L10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>246100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +940,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,56 +969,58 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>200</v>
       </c>
       <c r="N12" s="3">
         <v>200</v>
       </c>
       <c r="O12" s="3">
+        <v>200</v>
+      </c>
+      <c r="P12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>369000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1030,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1095,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1085,26 +1124,26 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1121,8 +1160,14 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1163,14 +1208,14 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>1600</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1225,14 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,56 +1251,58 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F17" s="3">
         <v>1500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>685700</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,56 +1312,62 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-156700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1377,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,8 +1406,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1352,45 +1419,45 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,56 +1467,62 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-163400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,23 +1532,29 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,11 +1576,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1518,56 +1597,62 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1662,14 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1615,11 +1706,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1636,8 +1727,14 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,56 +1792,62 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,56 +1857,62 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1922,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1987,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +2052,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2117,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,8 +2182,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2060,45 +2199,45 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>6800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,56 +2247,62 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2312,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,56 +2377,62 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,61 +2442,67 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2512,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2541,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,50 +2566,52 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2627,14 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2472,34 +2651,34 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>3000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>5100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>9100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2513,50 +2692,56 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,50 +2757,56 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F44" s="3">
         <v>2700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,8 +2822,14 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2690,50 +2887,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F46" s="3">
         <v>7000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2952,14 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2787,11 +2996,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2808,49 +3017,55 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>900</v>
       </c>
       <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>900</v>
+      </c>
+      <c r="P48" s="3">
+        <v>900</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2867,8 +3082,14 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2926,8 +3147,14 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3212,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,16 +3277,22 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -3082,11 +3321,11 @@
       <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>200</v>
+      </c>
+      <c r="P52" s="3">
+        <v>200</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3103,8 +3342,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,50 +3407,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F54" s="3">
         <v>8000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>11300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3472,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3501,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,50 +3526,52 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,28 +3587,34 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
@@ -3356,20 +3623,20 @@
         <v>600</v>
       </c>
       <c r="L58" s="3">
+        <v>600</v>
+      </c>
+      <c r="M58" s="3">
+        <v>600</v>
+      </c>
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,49 +3652,55 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3444,49 +3717,55 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M60" s="3">
-        <v>1800</v>
       </c>
       <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P60" s="3">
+        <v>1800</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
@@ -3503,50 +3782,56 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3562,8 +3847,14 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,10 +3865,10 @@
         <v>500</v>
       </c>
       <c r="F62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
@@ -3586,25 +3877,25 @@
         <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
+        <v>400</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3621,8 +3912,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3977,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +4042,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,50 +4107,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4172,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4201,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4262,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4327,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4392,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,50 +4457,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-14500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-14500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-12100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-12100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-10800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-10800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-10900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-10900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-10500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-10500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-8200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4522,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4587,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4652,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,50 +4717,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>600</v>
+      </c>
+      <c r="F76" s="3">
         <v>3500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4782,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,61 +4847,67 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,56 +4917,62 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-163500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4982,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,8 +5011,10 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4660,11 +5057,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4675,8 +5072,14 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +5137,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +5202,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5267,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5332,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,16 +5397,22 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-600</v>
+        <v>-1100</v>
       </c>
       <c r="E89" s="3">
-        <v>-600</v>
+        <v>-1100</v>
       </c>
       <c r="F89" s="3">
         <v>-600</v>
@@ -4988,38 +5421,38 @@
         <v>-600</v>
       </c>
       <c r="H89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5462,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,8 +5491,10 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5070,17 +5511,17 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5088,22 +5529,22 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5111,8 +5552,14 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5617,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,8 +5682,14 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5241,44 +5700,44 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>1500</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5747,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5776,10 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5349,11 +5816,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5370,8 +5837,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5902,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5967,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,22 +6032,28 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
@@ -5571,32 +6062,32 @@
         <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,8 +6097,14 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5644,20 +6141,20 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -5665,55 +6162,61 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -5722,6 +6225,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
